--- a/output/yearly_surface_area_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_92_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497632650099</v>
+        <v>10.84497634169909</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907192199894</v>
+        <v>37.78907197495639</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.760715602071037</v>
+        <v>4.100760160638926</v>
       </c>
       <c r="C2" t="n">
-        <v>5.859070298944964</v>
+        <v>10.81493270998286</v>
       </c>
       <c r="D2" t="n">
-        <v>27.95232063531519</v>
+        <v>35.934911218546</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.82563412373834</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C3" t="n">
-        <v>19.15389770985527</v>
+        <v>28.29887757491431</v>
       </c>
       <c r="D3" t="n">
-        <v>83.78725781894404</v>
+        <v>88.51928175341367</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.99309637500382</v>
+        <v>35.97810811753286</v>
       </c>
       <c r="C4" t="n">
-        <v>42.9210278819663</v>
+        <v>77.25274509947727</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7391364859027</v>
+        <v>108.2533923564788</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.8362787842316</v>
+        <v>44.69406423583604</v>
       </c>
       <c r="C5" t="n">
-        <v>88.28366230439444</v>
+        <v>102.4208292455485</v>
       </c>
       <c r="D5" t="n">
-        <v>77.65624340592271</v>
+        <v>71.34851440613696</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.46928506929254</v>
+        <v>38.60133798328035</v>
       </c>
       <c r="C6" t="n">
-        <v>107.7536827750172</v>
+        <v>90.96874227550947</v>
       </c>
       <c r="D6" t="n">
-        <v>51.56237117474674</v>
+        <v>47.25544399621598</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.2133266559246</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>84.32034682235003</v>
+        <v>74.79837583886024</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66300816219864</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.52557917913731</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C8" t="n">
-        <v>48.48361037422873</v>
+        <v>51.48775834922397</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -951,7 +951,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691115705253083</v>
+        <v>7.708378410571509</v>
       </c>
       <c r="C21" t="n">
-        <v>94.21616738935026</v>
+        <v>96.35473013214387</v>
       </c>
       <c r="D21" t="n">
-        <v>8.65250516840972</v>
+        <v>8.671925711892948</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.83554941177205</v>
+        <v>6.082908775513236</v>
       </c>
       <c r="C2" t="n">
-        <v>8.299695091702535</v>
+        <v>14.45623494503428</v>
       </c>
       <c r="D2" t="n">
-        <v>31.03500842665017</v>
+        <v>37.65296970097792</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.31298189567226</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C3" t="n">
-        <v>20.9603134856694</v>
+        <v>35.37236978401258</v>
       </c>
       <c r="D3" t="n">
-        <v>85.76547944300137</v>
+        <v>94.96445543179397</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.34219764708818</v>
+        <v>32.92781800043802</v>
       </c>
       <c r="C4" t="n">
-        <v>45.38423287192155</v>
+        <v>73.84509881803659</v>
       </c>
       <c r="D4" t="n">
-        <v>119.8036540969425</v>
+        <v>123.811148225678</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.26672624704821</v>
+        <v>48.94012305670351</v>
       </c>
       <c r="C5" t="n">
-        <v>82.88404993103698</v>
+        <v>121.0004045484194</v>
       </c>
       <c r="D5" t="n">
-        <v>95.79403224188253</v>
+        <v>91.49888603580274</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.73345731719294</v>
+        <v>49.1875234781737</v>
       </c>
       <c r="C6" t="n">
-        <v>123.7335901570425</v>
+        <v>125.5046630155038</v>
       </c>
       <c r="D6" t="n">
-        <v>61.98755004614362</v>
+        <v>56.83533809425636</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.29234949834984</v>
+        <v>35.63253292563798</v>
       </c>
       <c r="C7" t="n">
-        <v>117.6771885695439</v>
+        <v>101.3281440507218</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.70492021384499</v>
+        <v>20.77869016038374</v>
       </c>
       <c r="C8" t="n">
-        <v>78.85888434362504</v>
+        <v>74.68645660057609</v>
       </c>
       <c r="D8" t="n">
         <v>38.38633523605029</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31249886958674</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>48.92343334573128</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.874633519392515</v>
+        <v>7.89199861771696</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3545649420268</v>
+        <v>105.5554815119643</v>
       </c>
       <c r="D21" t="n">
-        <v>9.843291899240644</v>
+        <v>9.864998272146201</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.59444038715483</v>
+        <v>6.320491719940965</v>
       </c>
       <c r="C2" t="n">
-        <v>9.19701249338412</v>
+        <v>9.921542299118265</v>
       </c>
       <c r="D2" t="n">
-        <v>27.36719900358409</v>
+        <v>38.89488054685013</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.53587968226529</v>
+        <v>17.04804888424586</v>
       </c>
       <c r="C3" t="n">
-        <v>26.13412388705009</v>
+        <v>44.93459242337651</v>
       </c>
       <c r="D3" t="n">
-        <v>89.01997308257954</v>
+        <v>100.6733183319892</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.2611134982632</v>
+        <v>30.10725684613693</v>
       </c>
       <c r="C4" t="n">
-        <v>48.02611594404971</v>
+        <v>79.60108560803563</v>
       </c>
       <c r="D4" t="n">
-        <v>132.0048145653219</v>
+        <v>138.9477343297553</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.72109550766523</v>
+        <v>48.89103567149117</v>
       </c>
       <c r="C5" t="n">
-        <v>82.24591392327655</v>
+        <v>127.5535704742669</v>
       </c>
       <c r="D5" t="n">
-        <v>111.3301896615883</v>
+        <v>108.9249077861836</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.62278186852032</v>
+        <v>56.23156325614456</v>
       </c>
       <c r="C6" t="n">
-        <v>127.7185040885803</v>
+        <v>153.2380539127719</v>
       </c>
       <c r="D6" t="n">
-        <v>74.82782826998766</v>
+        <v>69.47435803872979</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.95216607106171</v>
+        <v>45.6934833987593</v>
       </c>
       <c r="C7" t="n">
-        <v>143.7877505116921</v>
+        <v>136.4216974867282</v>
       </c>
       <c r="D7" t="n">
-        <v>51.26293812495145</v>
+        <v>48.50815406683489</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.38495257771854</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9893432817654</v>
+        <v>99.9713687234527</v>
       </c>
       <c r="D8" t="n">
-        <v>41.47393176590651</v>
+        <v>41.0566889916016</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.63593583264045</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>67.67186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>36.78314123501524</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.043053265464096</v>
+        <v>8.058882237098373</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5973640583143</v>
+        <v>113.8317115990145</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05919824001313</v>
+        <v>11.08096307601026</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.54593383901924</v>
+        <v>5.790347959647687</v>
       </c>
       <c r="C2" t="n">
-        <v>6.180101798233672</v>
+        <v>6.746570223584081</v>
       </c>
       <c r="D2" t="n">
-        <v>22.5772519545639</v>
+        <v>31.88814718164065</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.37451320587032</v>
+        <v>20.75905520629881</v>
       </c>
       <c r="C3" t="n">
-        <v>38.2439818189345</v>
+        <v>61.43286259324416</v>
       </c>
       <c r="D3" t="n">
-        <v>97.14884407374313</v>
+        <v>109.1948884048515</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.1628155546515</v>
+        <v>23.4834050855837</v>
       </c>
       <c r="C4" t="n">
-        <v>68.25502739005525</v>
+        <v>107.9853752332194</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8869637830833</v>
+        <v>129.8479148590916</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.09181092477625</v>
+        <v>31.66136346195964</v>
       </c>
       <c r="C5" t="n">
-        <v>76.30634031258334</v>
+        <v>91.54797342101507</v>
       </c>
       <c r="D5" t="n">
-        <v>75.69274799742909</v>
+        <v>70.78400947619504</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.34095385747668</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>94.67189461592844</v>
+        <v>89.84169591103412</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73088762251191</v>
+        <v>31.91956310817655</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>79.4096448057075</v>
+        <v>70.30688009193108</v>
       </c>
       <c r="D7" t="n">
-        <v>29.16477905005999</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>49.48499303256047</v>
+        <v>49.81878725200438</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>26.90381408717959</v>
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.301838513560276</v>
+        <v>3.723769042208152</v>
       </c>
       <c r="C2" t="n">
-        <v>2.804853191033137</v>
+        <v>4.135121330287565</v>
       </c>
       <c r="D2" t="n">
-        <v>15.77766735495049</v>
+        <v>23.60121481009332</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35.77488634275377</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C3" t="n">
-        <v>31.57791490709866</v>
+        <v>44.69897297435728</v>
       </c>
       <c r="D3" t="n">
-        <v>93.69309215479436</v>
+        <v>109.7348496421872</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.2611134982632</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>83.45542709490861</v>
+        <v>132.6812387335479</v>
       </c>
       <c r="D4" t="n">
-        <v>144.7675347205304</v>
+        <v>152.0550479291545</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.68148144213009</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="C5" t="n">
-        <v>101.5863436969387</v>
+        <v>141.9607180340888</v>
       </c>
       <c r="D5" t="n">
-        <v>95.84311962709488</v>
+        <v>92.30882789180636</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.42524529132167</v>
+        <v>33.6906359666378</v>
       </c>
       <c r="C6" t="n">
-        <v>111.2153251801914</v>
+        <v>115.2404907676034</v>
       </c>
       <c r="D6" t="n">
-        <v>42.98876847355934</v>
+        <v>40.53341746523807</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>102.4061030299848</v>
+        <v>93.84231780583987</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>67.67677799225388</v>
+        <v>65.42366701100744</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>40.04843409934012</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
         <v>24.97566159603886</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.757950285407543</v>
+        <v>3.461642405174254</v>
       </c>
       <c r="C2" t="n">
-        <v>8.108254289374406</v>
+        <v>5.574363464713389</v>
       </c>
       <c r="D2" t="n">
-        <v>20.40955302358694</v>
+        <v>18.36653605104933</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.76520773443155</v>
+        <v>16.77806826557799</v>
       </c>
       <c r="C3" t="n">
-        <v>20.49398332615217</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D3" t="n">
-        <v>85.11261721967723</v>
+        <v>103.4811167661351</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.90071427981338</v>
+        <v>34.93156506480576</v>
       </c>
       <c r="C4" t="n">
-        <v>81.04327298557419</v>
+        <v>121.8584520419311</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4409158346525</v>
+        <v>169.1698556572891</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.84886157793756</v>
+        <v>40.2761995667254</v>
       </c>
       <c r="C5" t="n">
-        <v>127.7253763225101</v>
+        <v>193.6006472774711</v>
       </c>
       <c r="D5" t="n">
-        <v>122.7184630308513</v>
+        <v>120.215006385022</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.19381487502668</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C6" t="n">
-        <v>136.6946233485089</v>
+        <v>166.0380804807419</v>
       </c>
       <c r="D6" t="n">
-        <v>59.93471559656354</v>
+        <v>55.94980166502573</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.2551408965797</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>131.1516758103314</v>
+        <v>128.1573453123786</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.77315952705676</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>99.13688317484291</v>
+        <v>92.21065312138165</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>57.79843259212245</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.411573272257666</v>
+        <v>2.064615422031042</v>
       </c>
       <c r="C2" t="n">
-        <v>3.711006322052943</v>
+        <v>2.621266370338984</v>
       </c>
       <c r="D2" t="n">
-        <v>14.08317081742049</v>
+        <v>12.8206432697591</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.73928138349363</v>
+        <v>16.44918278465531</v>
       </c>
       <c r="C3" t="n">
-        <v>26.73298998664065</v>
+        <v>28.13198046519235</v>
       </c>
       <c r="D3" t="n">
-        <v>84.96535506404021</v>
+        <v>99.94682503084653</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62.09063355508952</v>
+        <v>38.45407582764332</v>
       </c>
       <c r="C4" t="n">
-        <v>77.80154206615123</v>
+        <v>116.3832450953466</v>
       </c>
       <c r="D4" t="n">
-        <v>166.3365317828329</v>
+        <v>181.3710161256685</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.83690067903736</v>
+        <v>42.46058820867456</v>
       </c>
       <c r="C5" t="n">
-        <v>151.7045639987384</v>
+        <v>231.9869825135214</v>
       </c>
       <c r="D5" t="n">
-        <v>133.3704256219292</v>
+        <v>127.283589855599</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.14348370020284</v>
+        <v>32.72459622565894</v>
       </c>
       <c r="C6" t="n">
-        <v>169.4192195741678</v>
+        <v>196.0255641069606</v>
       </c>
       <c r="D6" t="n">
-        <v>58.00263611460582</v>
+        <v>54.58124536530568</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.07902284242525</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>136.0623778269739</v>
+        <v>128.8759846318873</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>70.59747741238813</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>31.94999728700819</v>
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>2.84412309920301</v>
       </c>
       <c r="C2" t="n">
-        <v>5.907175936453058</v>
+        <v>3.141592653589793</v>
       </c>
       <c r="D2" t="n">
-        <v>15.24163310843173</v>
+        <v>12.48881254572368</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.90984344212531</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C3" t="n">
-        <v>20.40071729424872</v>
+        <v>18.90846078379357</v>
       </c>
       <c r="D3" t="n">
-        <v>77.27336180126645</v>
+        <v>89.31449739385357</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.90446134418112</v>
+        <v>35.50588747179015</v>
       </c>
       <c r="C4" t="n">
-        <v>72.19870791801469</v>
+        <v>94.73767171211296</v>
       </c>
       <c r="D4" t="n">
-        <v>170.1781105495506</v>
+        <v>187.9055288451353</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.72296119208249</v>
+        <v>49.1119289049467</v>
       </c>
       <c r="C5" t="n">
-        <v>149.0293015046659</v>
+        <v>225.7774282841603</v>
       </c>
       <c r="D5" t="n">
-        <v>157.9632056133118</v>
+        <v>155.2879431192393</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.10451689166923</v>
+        <v>42.30449032369931</v>
       </c>
       <c r="C6" t="n">
-        <v>205.4041999256305</v>
+        <v>272.3024519884166</v>
       </c>
       <c r="D6" t="n">
-        <v>80.94607996285377</v>
+        <v>74.58631833474294</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.19419042345839</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>183.9117791842592</v>
+        <v>195.1105752466026</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>118.2466022380071</v>
+        <v>110.402438081075</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3103,7 +3103,7 @@
         <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.365431130158066</v>
+        <v>1.921280257211008</v>
       </c>
       <c r="C2" t="n">
-        <v>3.490113088597411</v>
+        <v>2.623229865747478</v>
       </c>
       <c r="D2" t="n">
-        <v>10.88463679698439</v>
+        <v>10.19152291778614</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32922963828795</v>
+        <v>11.04466167277662</v>
       </c>
       <c r="C3" t="n">
-        <v>22.03041848329843</v>
+        <v>16.23810702824224</v>
       </c>
       <c r="D3" t="n">
-        <v>72.93894568701678</v>
+        <v>82.08392555207581</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.65072846812894</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="C4" t="n">
-        <v>64.17095694038852</v>
+        <v>76.64013453202725</v>
       </c>
       <c r="D4" t="n">
-        <v>170.7651956766902</v>
+        <v>189.5263943048467</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79.59519512181016</v>
+        <v>52.71985171805373</v>
       </c>
       <c r="C5" t="n">
-        <v>147.8266605669635</v>
+        <v>214.2664364518664</v>
       </c>
       <c r="D5" t="n">
-        <v>175.6837516749667</v>
+        <v>173.8184310368978</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.85800040691205</v>
+        <v>48.98626519880311</v>
       </c>
       <c r="C6" t="n">
-        <v>226.3753126360465</v>
+        <v>312.9968760771512</v>
       </c>
       <c r="D6" t="n">
-        <v>96.9259873448791</v>
+        <v>91.41151049012478</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>227.4493446244925</v>
+        <v>257.8118558737336</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>153.1280981698962</v>
+        <v>145.6177282324081</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>63.45624461169682</v>
+        <v>57.90937008270233</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39274013942773</v>
+        <v>3.673699909291564</v>
       </c>
       <c r="C2" t="n">
-        <v>8.368417430999811</v>
+        <v>7.322856125976958</v>
       </c>
       <c r="D2" t="n">
-        <v>14.02426595516569</v>
+        <v>22.29352686803657</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.95201753567892</v>
+        <v>8.8799079849124</v>
       </c>
       <c r="C3" t="n">
-        <v>18.04943154257761</v>
+        <v>13.49903093339364</v>
       </c>
       <c r="D3" t="n">
-        <v>66.04707680320416</v>
+        <v>73.09111658117503</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.05690997577986</v>
+        <v>26.52093248252334</v>
       </c>
       <c r="C4" t="n">
-        <v>59.85715752792803</v>
+        <v>60.82712425972387</v>
       </c>
       <c r="D4" t="n">
-        <v>168.2892279665797</v>
+        <v>187.2035792365988</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>78.76070957320037</v>
+        <v>51.0999680060465</v>
       </c>
       <c r="C5" t="n">
-        <v>134.6466976374501</v>
+        <v>183.4641022311227</v>
       </c>
       <c r="D5" t="n">
-        <v>189.1582389157542</v>
+        <v>194.1406085148068</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>82.43539123019619</v>
+        <v>56.55357650313753</v>
       </c>
       <c r="C6" t="n">
-        <v>230.7224914704514</v>
+        <v>324.7906112482681</v>
       </c>
       <c r="D6" t="n">
-        <v>121.3587424604695</v>
+        <v>114.3952059942469</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.16017341117502</v>
+        <v>29.8235317596096</v>
       </c>
       <c r="C7" t="n">
-        <v>269.1304251559951</v>
+        <v>333.0294379823072</v>
       </c>
       <c r="D7" t="n">
-        <v>59.88660995905543</v>
+        <v>55.99398031171683</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>213.9620946635499</v>
+        <v>218.8021108454866</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>110.7156155987298</v>
+        <v>102.2843663146582</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.652723354603888</v>
+        <v>4.596542751283566</v>
       </c>
       <c r="C2" t="n">
-        <v>2.755765805820797</v>
+        <v>4.91855599827652</v>
       </c>
       <c r="D2" t="n">
-        <v>13.71403368062369</v>
+        <v>10.15028951420777</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.818998569520092</v>
+        <v>2.654645792283375</v>
       </c>
       <c r="C2" t="n">
-        <v>4.685881792370026</v>
+        <v>4.217588137444298</v>
       </c>
       <c r="D2" t="n">
-        <v>10.32111361474672</v>
+        <v>16.58662746324986</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.66578917439536</v>
+        <v>12.33565990386117</v>
       </c>
       <c r="C3" t="n">
-        <v>25.28982086139784</v>
+        <v>19.86075605691298</v>
       </c>
       <c r="D3" t="n">
-        <v>72.24190481700154</v>
+        <v>81.2445312649448</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59.9720220093249</v>
+        <v>38.05843150283185</v>
       </c>
       <c r="C4" t="n">
-        <v>83.69791877785757</v>
+        <v>91.98092415858791</v>
       </c>
       <c r="D4" t="n">
-        <v>172.9093326627653</v>
+        <v>191.3514632870416</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.33282213840224</v>
+        <v>32.79037332184348</v>
       </c>
       <c r="C5" t="n">
-        <v>198.0921430244002</v>
+        <v>275.2084251929872</v>
       </c>
       <c r="D5" t="n">
-        <v>174.2602175038089</v>
+        <v>173.9411494999287</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.1635763181775</v>
+        <v>18.51576170209485</v>
       </c>
       <c r="C6" t="n">
-        <v>224.7249947452077</v>
+        <v>279.8295116368769</v>
       </c>
       <c r="D6" t="n">
-        <v>93.7461065308237</v>
+        <v>88.110874708447</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>150.4351642171472</v>
+        <v>153.8487009848134</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>81.61268665403733</v>
+        <v>75.35404503946393</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.427903130331368</v>
+        <v>5.899321954819084</v>
       </c>
       <c r="C2" t="n">
-        <v>5.540984042768997</v>
+        <v>2.644828315240907</v>
       </c>
       <c r="D2" t="n">
-        <v>22.36617619815084</v>
+        <v>14.68989089864502</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24792450528471</v>
+        <v>9.768389657255764</v>
       </c>
       <c r="C3" t="n">
-        <v>6.940956269024949</v>
+        <v>12.39456476611598</v>
       </c>
       <c r="D3" t="n">
-        <v>14.65749322440488</v>
+        <v>11.66316272645211</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39786075625111</v>
+        <v>13.39862632284947</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14174160625582</v>
+        <v>70.14574957256485</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576218912500131</v>
+        <v>1.576308979158761</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.703954161673968</v>
+        <v>4.310854169347744</v>
       </c>
       <c r="C2" t="n">
-        <v>4.959789401854886</v>
+        <v>4.634830911749192</v>
       </c>
       <c r="D2" t="n">
-        <v>26.54056743660827</v>
+        <v>16.49237968364217</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.93224371287374</v>
+        <v>16.11047982669016</v>
       </c>
       <c r="C3" t="n">
-        <v>16.11538856521139</v>
+        <v>11.07902284242526</v>
       </c>
       <c r="D3" t="n">
-        <v>29.89912633283661</v>
+        <v>21.18120671912493</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.78672406846696</v>
+        <v>11.46092269937727</v>
       </c>
       <c r="C4" t="n">
-        <v>11.15461741565226</v>
+        <v>19.73116535995239</v>
       </c>
       <c r="D4" t="n">
-        <v>22.75593003673682</v>
+        <v>21.18611545764617</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44016062434109</v>
+        <v>15.44406836637785</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13984348316612</v>
+        <v>86.16164457031851</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25056013144023</v>
+        <v>3.251382813974284</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.538038799656257</v>
+        <v>4.734969177582366</v>
       </c>
       <c r="C2" t="n">
-        <v>8.404742096056944</v>
+        <v>5.943500601510189</v>
       </c>
       <c r="D2" t="n">
-        <v>23.72098803001143</v>
+        <v>24.75771360569606</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.70505908256523</v>
+        <v>15.4821612959722</v>
       </c>
       <c r="C3" t="n">
-        <v>18.04452280405637</v>
+        <v>15.29562923216531</v>
       </c>
       <c r="D3" t="n">
-        <v>44.19337290667017</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.27691927252238</v>
+        <v>22.90908267859932</v>
       </c>
       <c r="C4" t="n">
-        <v>28.33323874456295</v>
+        <v>24.26193101505142</v>
       </c>
       <c r="D4" t="n">
-        <v>32.6087499965578</v>
+        <v>26.84000048640355</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.97794388661684</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C5" t="n">
-        <v>14.03899217072939</v>
+        <v>23.39013905368026</v>
       </c>
       <c r="D5" t="n">
-        <v>30.82687791334985</v>
+        <v>30.43417883165113</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73313742691241</v>
+        <v>16.74342789418593</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0721383041657</v>
+        <v>102.1349101545342</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019941228073724</v>
+        <v>5.023028368255781</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.454009407718531</v>
+        <v>5.734388340505619</v>
       </c>
       <c r="C2" t="n">
-        <v>6.055419839794326</v>
+        <v>5.582217446347364</v>
       </c>
       <c r="D2" t="n">
-        <v>18.84955592153876</v>
+        <v>39.73623832938965</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.75767254796706</v>
+        <v>15.88958659323463</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44828315240908</v>
+        <v>19.86075605691298</v>
       </c>
       <c r="D3" t="n">
-        <v>52.39096623713104</v>
+        <v>41.71936869196821</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.68005772606933</v>
+        <v>26.64855968407542</v>
       </c>
       <c r="C4" t="n">
-        <v>37.72660077879643</v>
+        <v>32.23863111205676</v>
       </c>
       <c r="D4" t="n">
-        <v>46.62221672697677</v>
+        <v>34.82946330356409</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.05406254365837</v>
+        <v>22.70291566070749</v>
       </c>
       <c r="C5" t="n">
-        <v>34.55751918948773</v>
+        <v>34.95021827118646</v>
       </c>
       <c r="D5" t="n">
-        <v>35.09748042682348</v>
+        <v>33.35487825178539</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.8063179648229</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="C6" t="n">
-        <v>17.50947030524187</v>
+        <v>25.60005313593983</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05937211945893</v>
+        <v>18.07809061332207</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8159038269464</v>
+        <v>117.9380197154821</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879760807412928</v>
+        <v>6.886891662217932</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.410231671654924</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C2" t="n">
-        <v>4.468915549731481</v>
+        <v>11.00048302608551</v>
       </c>
       <c r="D2" t="n">
-        <v>34.62722327648925</v>
+        <v>34.96985322527139</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="C3" t="n">
-        <v>23.26742059064941</v>
+        <v>19.68895020866978</v>
       </c>
       <c r="D3" t="n">
-        <v>51.80682635310419</v>
+        <v>58.91958847037233</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.15906849028376</v>
+        <v>21.22440361811179</v>
       </c>
       <c r="C4" t="n">
-        <v>44.63123238276425</v>
+        <v>35.36549755008285</v>
       </c>
       <c r="D4" t="n">
-        <v>53.30988208830605</v>
+        <v>40.90451809744336</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.75262494072559</v>
+        <v>19.24225500323749</v>
       </c>
       <c r="C5" t="n">
-        <v>39.98167525545136</v>
+        <v>35.76016012719008</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66198535676539</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.81890075852886</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="C6" t="n">
-        <v>24.95602664195392</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>15.09142570968197</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059338928289694</v>
+        <v>7.0688619064281</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18130245271588</v>
+        <v>67.15418811106694</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294504196217271</v>
+        <v>5.301646429821075</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.332673603019426</v>
+        <v>5.05403718146258</v>
       </c>
       <c r="C2" t="n">
-        <v>2.886338250485622</v>
+        <v>8.442048508818322</v>
       </c>
       <c r="D2" t="n">
-        <v>30.48522971227195</v>
+        <v>34.91880234465055</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.2232419439583</v>
+        <v>20.85232123820225</v>
       </c>
       <c r="C3" t="n">
-        <v>19.70367642423349</v>
+        <v>34.96494448675016</v>
       </c>
       <c r="D3" t="n">
-        <v>69.75808312525712</v>
+        <v>74.8877148799467</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.36175048571511</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="C4" t="n">
-        <v>52.86318688287376</v>
+        <v>44.35045253934966</v>
       </c>
       <c r="D4" t="n">
-        <v>67.5786032218292</v>
+        <v>63.36690557061038</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.04839304161113</v>
+        <v>26.94897448157495</v>
       </c>
       <c r="C5" t="n">
-        <v>66.41523219229673</v>
+        <v>54.19247327442395</v>
       </c>
       <c r="D5" t="n">
-        <v>48.03200643027521</v>
+        <v>39.80986940720817</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.85414586489051</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="C6" t="n">
-        <v>48.02022545782425</v>
+        <v>45.12210623488766</v>
       </c>
       <c r="D6" t="n">
-        <v>36.06548366321083</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.53437385074653</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>27.60772719112455</v>
+        <v>32.27888276793088</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>19.86075605691297</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
         <v>24.91184799526281</v>
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282425733367842</v>
+        <v>7.295183926518287</v>
       </c>
       <c r="C21" t="n">
-        <v>75.55516698369136</v>
+        <v>77.51132921925679</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372122516696861</v>
+        <v>6.3832859357035</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.291039288813561</v>
+        <v>3.923063826170254</v>
       </c>
       <c r="C2" t="n">
-        <v>5.848271074198249</v>
+        <v>6.249805885235195</v>
       </c>
       <c r="D2" t="n">
-        <v>30.48228446915921</v>
+        <v>29.04991456866312</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.46024405130928</v>
+        <v>18.98700060013331</v>
       </c>
       <c r="C3" t="n">
-        <v>14.56422719250143</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D3" t="n">
-        <v>77.96058519423921</v>
+        <v>85.44641143912115</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.98560224626834</v>
+        <v>35.49312475163494</v>
       </c>
       <c r="C4" t="n">
-        <v>50.8339143781956</v>
+        <v>70.23324901411257</v>
       </c>
       <c r="D4" t="n">
-        <v>87.36081946240242</v>
+        <v>86.04625928641595</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.71231653158924</v>
+        <v>35.19565519724816</v>
       </c>
       <c r="C5" t="n">
-        <v>83.66944809443443</v>
+        <v>70.36676670189014</v>
       </c>
       <c r="D5" t="n">
-        <v>61.04016351154545</v>
+        <v>54.33973543006097</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.56108632740622</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>80.18129850124551</v>
+        <v>68.10580173900973</v>
       </c>
       <c r="D6" t="n">
-        <v>43.31078172055229</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.3139636433765</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>50.783845245279</v>
+        <v>50.36463897556562</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>24.62812290873548</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.493497236282693</v>
+        <v>7.508775262041696</v>
       </c>
       <c r="C21" t="n">
-        <v>85.23853106271564</v>
+        <v>87.2895124212347</v>
       </c>
       <c r="D21" t="n">
-        <v>7.493497236282693</v>
+        <v>7.508775262041696</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_92_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634169909</v>
+        <v>10.84497633864866</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907197495639</v>
+        <v>37.78907196432722</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.100760160638926</v>
+        <v>6.883033154474388</v>
       </c>
       <c r="C2" t="n">
-        <v>10.81493270998286</v>
+        <v>4.297109701488289</v>
       </c>
       <c r="D2" t="n">
-        <v>35.934911218546</v>
+        <v>31.51508305402686</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.95340019401067</v>
+        <v>21.91751749731004</v>
       </c>
       <c r="C3" t="n">
-        <v>28.29887757491431</v>
+        <v>20.2829075697391</v>
       </c>
       <c r="D3" t="n">
-        <v>88.51928175341367</v>
+        <v>74.25939634922874</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.97810811753286</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="C4" t="n">
-        <v>77.25274509947727</v>
+        <v>50.13196476965913</v>
       </c>
       <c r="D4" t="n">
-        <v>108.2533923564788</v>
+        <v>86.86307337634929</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.69406423583604</v>
+        <v>50.53546307610458</v>
       </c>
       <c r="C5" t="n">
-        <v>102.4208292455485</v>
+        <v>82.56498192715677</v>
       </c>
       <c r="D5" t="n">
-        <v>71.34851440613696</v>
+        <v>63.61725123519332</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.60133798328035</v>
+        <v>49.42903341341842</v>
       </c>
       <c r="C6" t="n">
-        <v>90.96874227550947</v>
+        <v>113.0669013504009</v>
       </c>
       <c r="D6" t="n">
-        <v>47.25544399621598</v>
+        <v>45.36361617013237</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>37.00992495469625</v>
       </c>
       <c r="C7" t="n">
-        <v>74.79837583886024</v>
+        <v>91.3869667975186</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>19.10971906316416</v>
       </c>
       <c r="C8" t="n">
-        <v>51.48775834922397</v>
+        <v>54.07466354991431</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>35.01894061048373</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.708378410571509</v>
+        <v>7.702243244910774</v>
       </c>
       <c r="C21" t="n">
-        <v>96.35473013214387</v>
+        <v>95.31526015577083</v>
       </c>
       <c r="D21" t="n">
-        <v>8.671925711892948</v>
+        <v>8.665023650524621</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.082908775513236</v>
+        <v>8.809222150206629</v>
       </c>
       <c r="C2" t="n">
-        <v>14.45623494503428</v>
+        <v>5.188536616944393</v>
       </c>
       <c r="D2" t="n">
-        <v>37.65296970097792</v>
+        <v>27.10212712343744</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.77039421039326</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C3" t="n">
-        <v>35.37236978401258</v>
+        <v>18.30468594568178</v>
       </c>
       <c r="D3" t="n">
-        <v>94.96445543179397</v>
+        <v>80.5965777801419</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.92781800043802</v>
+        <v>41.64475586644545</v>
       </c>
       <c r="C4" t="n">
-        <v>73.84509881803659</v>
+        <v>49.87671036655495</v>
       </c>
       <c r="D4" t="n">
-        <v>123.811148225678</v>
+        <v>100.7106247447505</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.94012305670351</v>
+        <v>55.76326960121884</v>
       </c>
       <c r="C5" t="n">
-        <v>121.0004045484194</v>
+        <v>87.47372044839082</v>
       </c>
       <c r="D5" t="n">
-        <v>91.49888603580274</v>
+        <v>78.53981633974485</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.1875234781737</v>
+        <v>58.48565598509524</v>
       </c>
       <c r="C6" t="n">
-        <v>125.5046630155038</v>
+        <v>121.1172325252248</v>
       </c>
       <c r="D6" t="n">
-        <v>56.83533809425636</v>
+        <v>53.33344403320799</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.63253292563798</v>
+        <v>48.02906118716245</v>
       </c>
       <c r="C7" t="n">
-        <v>101.3281440507218</v>
+        <v>126.7200666733613</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.77869016038374</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="C8" t="n">
-        <v>74.68645660057609</v>
+        <v>86.28580572625216</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>13.7562488319063</v>
       </c>
       <c r="C9" t="n">
-        <v>48.92343334573128</v>
+        <v>49.36718330805084</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
         <v>35.44600086183109</v>
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.89199861771696</v>
+        <v>7.887891927126004</v>
       </c>
       <c r="C21" t="n">
-        <v>105.5554815119643</v>
+        <v>104.5145680344196</v>
       </c>
       <c r="D21" t="n">
-        <v>9.864998272146201</v>
+        <v>9.859864908907506</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.320491719940965</v>
+        <v>9.659415662084367</v>
       </c>
       <c r="C2" t="n">
-        <v>9.921542299118265</v>
+        <v>7.204064653763095</v>
       </c>
       <c r="D2" t="n">
-        <v>38.89488054685013</v>
+        <v>27.02064206398496</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.04804888424586</v>
+        <v>25.42235680147115</v>
       </c>
       <c r="C3" t="n">
-        <v>44.93459242337651</v>
+        <v>19.06554041647306</v>
       </c>
       <c r="D3" t="n">
-        <v>100.6733183319892</v>
+        <v>82.33427121665875</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.10725684613693</v>
+        <v>41.4150269036517</v>
       </c>
       <c r="C4" t="n">
-        <v>79.60108560803563</v>
+        <v>47.32416633551325</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9477343297553</v>
+        <v>113.3967685790278</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.89103567149117</v>
+        <v>58.38944471007906</v>
       </c>
       <c r="C5" t="n">
-        <v>127.5535704742669</v>
+        <v>89.36358477906593</v>
       </c>
       <c r="D5" t="n">
-        <v>108.9249077861836</v>
+        <v>93.83053683338892</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.23156325614456</v>
+        <v>66.37498053642261</v>
       </c>
       <c r="C6" t="n">
-        <v>153.2380539127719</v>
+        <v>128.2417756149439</v>
       </c>
       <c r="D6" t="n">
-        <v>69.47435803872979</v>
+        <v>62.95358978712248</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.6934833987593</v>
+        <v>57.3713723407751</v>
       </c>
       <c r="C7" t="n">
-        <v>136.4216974867282</v>
+        <v>149.1775454080071</v>
       </c>
       <c r="D7" t="n">
-        <v>48.50815406683489</v>
+        <v>47.4301950875719</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.12216298814988</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="C8" t="n">
-        <v>99.9713687234527</v>
+        <v>121.6679929873072</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>74.43905617910588</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.058882237098373</v>
+        <v>8.059200660562123</v>
       </c>
       <c r="C21" t="n">
-        <v>113.8317115990145</v>
+        <v>112.8288092478697</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08096307601026</v>
+        <v>11.08140090827292</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.790347959647687</v>
+        <v>8.779769719079225</v>
       </c>
       <c r="C2" t="n">
-        <v>6.746570223584081</v>
+        <v>4.78307481509046</v>
       </c>
       <c r="D2" t="n">
-        <v>31.88814718164065</v>
+        <v>22.03238197870692</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.75905520629881</v>
+        <v>30.03166227290993</v>
       </c>
       <c r="C3" t="n">
-        <v>61.43286259324416</v>
+        <v>30.36545649235384</v>
       </c>
       <c r="D3" t="n">
-        <v>109.1948884048515</v>
+        <v>89.9379071860503</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.4834050855837</v>
+        <v>28.05245890114836</v>
       </c>
       <c r="C4" t="n">
-        <v>107.9853752332194</v>
+        <v>71.40741926839175</v>
       </c>
       <c r="D4" t="n">
-        <v>129.8479148590916</v>
+        <v>108.3682568378757</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.66136346195964</v>
+        <v>37.38004383919731</v>
       </c>
       <c r="C5" t="n">
-        <v>91.54797342101507</v>
+        <v>76.62540831646356</v>
       </c>
       <c r="D5" t="n">
-        <v>70.78400947619504</v>
+        <v>63.73996969822418</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>35.62271544859552</v>
       </c>
       <c r="C6" t="n">
-        <v>89.84169591103412</v>
+        <v>98.25429198872504</v>
       </c>
       <c r="D6" t="n">
-        <v>31.91956310817655</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>70.30688009193108</v>
+        <v>85.51807902153115</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>49.81878725200438</v>
+        <v>54.82570054366312</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.723769042208152</v>
+        <v>5.291620125890307</v>
       </c>
       <c r="C2" t="n">
-        <v>4.135121330287565</v>
+        <v>2.462223242251</v>
       </c>
       <c r="D2" t="n">
-        <v>23.60121481009332</v>
+        <v>16.69167446760427</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.93576979306323</v>
+        <v>31.12140222462389</v>
       </c>
       <c r="C3" t="n">
-        <v>44.69897297435728</v>
+        <v>24.71549845441345</v>
       </c>
       <c r="D3" t="n">
-        <v>109.7348496421872</v>
+        <v>88.38674581334034</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63052837250048</v>
+        <v>41.63199314629023</v>
       </c>
       <c r="C4" t="n">
-        <v>132.6812387335479</v>
+        <v>76.28277836768142</v>
       </c>
       <c r="D4" t="n">
-        <v>152.0550479291545</v>
+        <v>126.4147431373405</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.04839304161113</v>
+        <v>41.30703465618456</v>
       </c>
       <c r="C5" t="n">
-        <v>141.9607180340888</v>
+        <v>104.3352372688298</v>
       </c>
       <c r="D5" t="n">
-        <v>92.30882789180636</v>
+        <v>81.06781667818038</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.6906359666378</v>
+        <v>42.98876847355934</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2404907676034</v>
+        <v>112.9863980386527</v>
       </c>
       <c r="D6" t="n">
-        <v>40.53341746523807</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>93.84231780583987</v>
+        <v>110.251248934621</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>65.42366701100744</v>
+        <v>73.60162538738336</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>41.3796839862988</v>
       </c>
       <c r="D9" t="n">
         <v>28.73281006019139</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.461642405174254</v>
+        <v>5.607742886657781</v>
       </c>
       <c r="C2" t="n">
-        <v>5.574363464713389</v>
+        <v>6.498188054409638</v>
       </c>
       <c r="D2" t="n">
-        <v>18.36653605104933</v>
+        <v>15.5911352911436</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.77806826557799</v>
+        <v>24.42588288166064</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6242369756475</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="D3" t="n">
-        <v>103.4811167661351</v>
+        <v>81.59305169995241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.93156506480576</v>
+        <v>50.92325341928206</v>
       </c>
       <c r="C4" t="n">
-        <v>121.8584520419311</v>
+        <v>68.57409539393547</v>
       </c>
       <c r="D4" t="n">
-        <v>169.1698556572891</v>
+        <v>140.4282098677595</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.2761995667254</v>
+        <v>51.32086123950202</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6006472774711</v>
+        <v>123.8965602759475</v>
       </c>
       <c r="D5" t="n">
-        <v>120.215006385022</v>
+        <v>105.0470043544087</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.25165587411923</v>
+        <v>49.34853010167018</v>
       </c>
       <c r="C6" t="n">
-        <v>166.0380804807419</v>
+        <v>138.6267028304666</v>
       </c>
       <c r="D6" t="n">
-        <v>55.94980166502573</v>
+        <v>52.72966919509619</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="C7" t="n">
-        <v>128.1573453123786</v>
+        <v>137.3199966361141</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="C8" t="n">
-        <v>92.21065312138165</v>
+        <v>107.9824299901067</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>63.89999457401638</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.064615422031042</v>
+        <v>3.28100082759284</v>
       </c>
       <c r="C2" t="n">
-        <v>2.621266370338984</v>
+        <v>2.946224860444678</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8206432697591</v>
+        <v>10.80413348523615</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44918278465531</v>
+        <v>24.64186737659494</v>
       </c>
       <c r="C3" t="n">
-        <v>28.13198046519235</v>
+        <v>21.55427084673872</v>
       </c>
       <c r="D3" t="n">
-        <v>99.94682503084653</v>
+        <v>79.2270397327176</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.45407582764332</v>
+        <v>55.93900244027901</v>
       </c>
       <c r="C4" t="n">
-        <v>116.3832450953466</v>
+        <v>64.82185566830415</v>
       </c>
       <c r="D4" t="n">
-        <v>181.3710161256685</v>
+        <v>149.7832837415274</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.46058820867456</v>
+        <v>53.8979489631499</v>
       </c>
       <c r="C5" t="n">
-        <v>231.9869825135214</v>
+        <v>142.279786037969</v>
       </c>
       <c r="D5" t="n">
-        <v>127.283589855599</v>
+        <v>114.3490638521473</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.72459622565894</v>
+        <v>43.27053006467818</v>
       </c>
       <c r="C6" t="n">
-        <v>196.0255641069606</v>
+        <v>174.4909282143069</v>
       </c>
       <c r="D6" t="n">
-        <v>54.58124536530568</v>
+        <v>51.92463607761381</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>128.8759846318873</v>
+        <v>145.0453693208322</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>70.59747741238813</v>
+        <v>81.94648087348126</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
         <v>9.506263020221864</v>
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.84412309920301</v>
+        <v>4.329507375728434</v>
       </c>
       <c r="C2" t="n">
-        <v>3.141592653589793</v>
+        <v>7.085273181549231</v>
       </c>
       <c r="D2" t="n">
-        <v>12.48881254572368</v>
+        <v>10.7422833798686</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.849694790259</v>
+        <v>18.02979658849267</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90846078379357</v>
+        <v>16.26265072084841</v>
       </c>
       <c r="D3" t="n">
-        <v>89.31449739385357</v>
+        <v>70.90672793922589</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.50588747179015</v>
+        <v>51.91874559138832</v>
       </c>
       <c r="C4" t="n">
-        <v>94.73767171211296</v>
+        <v>59.16797063954677</v>
       </c>
       <c r="D4" t="n">
-        <v>187.9055288451353</v>
+        <v>154.3906257175576</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.1119289049467</v>
+        <v>68.18237805994099</v>
       </c>
       <c r="C5" t="n">
-        <v>225.7774282841603</v>
+        <v>132.3886779176824</v>
       </c>
       <c r="D5" t="n">
-        <v>155.2879431192393</v>
+        <v>137.5428533649782</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.30449032369931</v>
+        <v>55.30577517103983</v>
       </c>
       <c r="C6" t="n">
-        <v>272.3024519884166</v>
+        <v>200.4934979089879</v>
       </c>
       <c r="D6" t="n">
-        <v>74.58631833474294</v>
+        <v>71.24543089719104</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>195.1105752466026</v>
+        <v>196.0687610059475</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>110.402438081075</v>
+        <v>129.4287085893783</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>58.13124506386212</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.921280257211008</v>
+        <v>3.34579617607313</v>
       </c>
       <c r="C2" t="n">
-        <v>2.623229865747478</v>
+        <v>4.567090320156161</v>
       </c>
       <c r="D2" t="n">
-        <v>10.19152291778614</v>
+        <v>8.465610453720245</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.04466167277662</v>
+        <v>16.8516993433965</v>
       </c>
       <c r="C3" t="n">
-        <v>16.23810702824224</v>
+        <v>21.90279128174634</v>
       </c>
       <c r="D3" t="n">
-        <v>82.08392555207581</v>
+        <v>65.41384953396498</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.46010518258904</v>
+        <v>46.39248776418302</v>
       </c>
       <c r="C4" t="n">
-        <v>76.64013453202725</v>
+        <v>52.3399153565102</v>
       </c>
       <c r="D4" t="n">
-        <v>189.5263943048467</v>
+        <v>155.1946770873358</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.71985171805373</v>
+        <v>73.95014582239101</v>
       </c>
       <c r="C5" t="n">
-        <v>214.2664364518664</v>
+        <v>127.5535704742669</v>
       </c>
       <c r="D5" t="n">
-        <v>173.8184310368978</v>
+        <v>153.0299233994716</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.98626519880311</v>
+        <v>66.49573550404497</v>
       </c>
       <c r="C6" t="n">
-        <v>312.9968760771512</v>
+        <v>214.2998158738108</v>
       </c>
       <c r="D6" t="n">
-        <v>91.41151049012478</v>
+        <v>87.26558993509049</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>257.8118558737336</v>
+        <v>236.4323361183508</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>44.85507085933252</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>145.6177282324081</v>
+        <v>167.3978010511236</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>71.77655640518853</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.673699909291564</v>
+        <v>5.470298208063228</v>
       </c>
       <c r="C2" t="n">
-        <v>7.322856125976958</v>
+        <v>6.89775937003809</v>
       </c>
       <c r="D2" t="n">
-        <v>22.29352686803657</v>
+        <v>8.706138641260715</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.8799079849124</v>
+        <v>14.11753198706914</v>
       </c>
       <c r="C3" t="n">
-        <v>13.49903093339364</v>
+        <v>19.72822011683965</v>
       </c>
       <c r="D3" t="n">
-        <v>73.09111658117503</v>
+        <v>58.16364273810228</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.52093248252334</v>
+        <v>39.47509344006</v>
       </c>
       <c r="C4" t="n">
-        <v>60.82712425972387</v>
+        <v>53.32264480846126</v>
       </c>
       <c r="D4" t="n">
-        <v>187.2035792365988</v>
+        <v>152.7569975376909</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.0999680060465</v>
+        <v>73.14020396638739</v>
       </c>
       <c r="C5" t="n">
-        <v>183.4641022311227</v>
+        <v>113.2691413774758</v>
       </c>
       <c r="D5" t="n">
-        <v>194.1406085148068</v>
+        <v>169.3023915973625</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.55357650313753</v>
+        <v>79.98004022187492</v>
       </c>
       <c r="C6" t="n">
-        <v>324.7906112482681</v>
+        <v>212.3274847359789</v>
       </c>
       <c r="D6" t="n">
-        <v>114.3952059942469</v>
+        <v>108.1159476778843</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.8235317596096</v>
+        <v>44.13643153982385</v>
       </c>
       <c r="C7" t="n">
-        <v>333.0294379823072</v>
+        <v>268.5914456663636</v>
       </c>
       <c r="D7" t="n">
-        <v>55.99398031171683</v>
+        <v>55.21545438224911</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>12.85107744859075</v>
       </c>
       <c r="C8" t="n">
-        <v>218.8021108454866</v>
+        <v>229.31662875797</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>102.2843663146582</v>
+        <v>124.1390519588964</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.596542751283566</v>
+        <v>8.097455064627692</v>
       </c>
       <c r="C2" t="n">
-        <v>4.91855599827652</v>
+        <v>3.887720908817369</v>
       </c>
       <c r="D2" t="n">
-        <v>10.15028951420777</v>
+        <v>6.026949156371169</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.654645792283375</v>
+        <v>3.829797794266807</v>
       </c>
       <c r="C2" t="n">
-        <v>4.217588137444298</v>
+        <v>3.808199344773377</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58662746324986</v>
+        <v>6.406885517914684</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.33565990386117</v>
+        <v>19.39933463591697</v>
       </c>
       <c r="C3" t="n">
-        <v>19.86075605691298</v>
+        <v>25.02965771977243</v>
       </c>
       <c r="D3" t="n">
-        <v>81.2445312649448</v>
+        <v>62.00718500022854</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.05843150283185</v>
+        <v>55.23705283174254</v>
       </c>
       <c r="C4" t="n">
-        <v>91.98092415858791</v>
+        <v>74.54704842657306</v>
       </c>
       <c r="D4" t="n">
-        <v>191.3514632870416</v>
+        <v>158.1301027230338</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.79037332184348</v>
+        <v>48.42470551197393</v>
       </c>
       <c r="C5" t="n">
-        <v>275.2084251929872</v>
+        <v>175.0701593598125</v>
       </c>
       <c r="D5" t="n">
-        <v>173.9411494999287</v>
+        <v>155.1652246562084</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.51576170209485</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="C6" t="n">
-        <v>279.8295116368769</v>
+        <v>222.6721602956276</v>
       </c>
       <c r="D6" t="n">
-        <v>88.110874708447</v>
+        <v>85.29325879725866</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8487009848134</v>
+        <v>161.2746406197363</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>75.35404503946393</v>
+        <v>91.45961612763286</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.899321954819084</v>
+        <v>7.483862749473436</v>
       </c>
       <c r="C2" t="n">
-        <v>2.644828315240907</v>
+        <v>4.636794407157685</v>
       </c>
       <c r="D2" t="n">
-        <v>14.68989089864502</v>
+        <v>17.18353006743192</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.768389657255764</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="C3" t="n">
-        <v>12.39456476611598</v>
+        <v>9.950012982541423</v>
       </c>
       <c r="D3" t="n">
-        <v>11.66316272645211</v>
+        <v>8.197593330460867</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39862632284947</v>
+        <v>13.39891066391973</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14574957256485</v>
+        <v>70.14723818169743</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576308979158761</v>
+        <v>1.57634243104938</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.310854169347744</v>
+        <v>5.557673753741193</v>
       </c>
       <c r="C2" t="n">
-        <v>4.634830911749192</v>
+        <v>6.290057541109315</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49237968364217</v>
+        <v>13.90841972606456</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11047982669016</v>
+        <v>22.44275251908209</v>
       </c>
       <c r="C3" t="n">
-        <v>11.07902284242526</v>
+        <v>15.0354660905399</v>
       </c>
       <c r="D3" t="n">
-        <v>21.18120671912493</v>
+        <v>20.65106295883166</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.46092269937727</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C4" t="n">
-        <v>19.73116535995239</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="D4" t="n">
-        <v>21.18611545764617</v>
+        <v>19.36104647545135</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44406836637785</v>
+        <v>15.44294571924592</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16164457031851</v>
+        <v>86.15538138105622</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251382813974284</v>
+        <v>3.251146467209669</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.734969177582366</v>
+        <v>5.764822519337271</v>
       </c>
       <c r="C2" t="n">
-        <v>5.943500601510189</v>
+        <v>8.751299035656068</v>
       </c>
       <c r="D2" t="n">
-        <v>24.75771360569606</v>
+        <v>29.51428123277186</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4821612959722</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="C3" t="n">
-        <v>15.29562923216531</v>
+        <v>20.75905520629881</v>
       </c>
       <c r="D3" t="n">
-        <v>29.45733986592554</v>
+        <v>26.98333565122358</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.90908267859932</v>
+        <v>33.14478424307656</v>
       </c>
       <c r="C4" t="n">
-        <v>24.26193101505142</v>
+        <v>28.61401858797754</v>
       </c>
       <c r="D4" t="n">
-        <v>26.84000048640355</v>
+        <v>25.35952494839936</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.52924412804704</v>
+        <v>17.13149743910684</v>
       </c>
       <c r="C5" t="n">
-        <v>23.39013905368026</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
         <v>12.19625172985813</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74342789418593</v>
+        <v>16.73980098587779</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1349101545342</v>
+        <v>102.1127860138545</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023028368255781</v>
+        <v>5.021940295763338</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.734388340505619</v>
+        <v>5.578290455530377</v>
       </c>
       <c r="C2" t="n">
-        <v>5.582217446347364</v>
+        <v>4.82921695719006</v>
       </c>
       <c r="D2" t="n">
-        <v>39.73623832938965</v>
+        <v>21.74571164906685</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.88958659323463</v>
+        <v>20.15528036818702</v>
       </c>
       <c r="C3" t="n">
-        <v>19.86075605691298</v>
+        <v>28.36759991421159</v>
       </c>
       <c r="D3" t="n">
-        <v>41.71936869196821</v>
+        <v>43.41288348179395</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.64855968407542</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>32.23863111205676</v>
+        <v>41.37673874318607</v>
       </c>
       <c r="D4" t="n">
-        <v>34.82946330356409</v>
+        <v>32.7491399182651</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.70291566070749</v>
+        <v>33.28124717396688</v>
       </c>
       <c r="C5" t="n">
-        <v>34.95021827118646</v>
+        <v>37.50276230222816</v>
       </c>
       <c r="D5" t="n">
-        <v>33.35487825178539</v>
+        <v>31.56318869153496</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.10316562440393</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C6" t="n">
-        <v>25.60005313593983</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,7 +5532,7 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07809061332207</v>
+        <v>18.06815078394659</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9380197154821</v>
+        <v>117.8731741619373</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886891662217932</v>
+        <v>6.883105060551082</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.725953521794898</v>
+        <v>6.813329067472864</v>
       </c>
       <c r="C2" t="n">
-        <v>11.00048302608551</v>
+        <v>2.895173979823844</v>
       </c>
       <c r="D2" t="n">
-        <v>34.96985322527139</v>
+        <v>24.46024405130928</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1448409963388</v>
+        <v>17.62728002975148</v>
       </c>
       <c r="C3" t="n">
-        <v>19.68895020866978</v>
+        <v>21.47082229187775</v>
       </c>
       <c r="D3" t="n">
-        <v>58.91958847037233</v>
+        <v>47.30551312913256</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.22440361811179</v>
+        <v>27.58023825540564</v>
       </c>
       <c r="C4" t="n">
-        <v>35.36549755008285</v>
+        <v>48.20479402622264</v>
       </c>
       <c r="D4" t="n">
-        <v>40.90451809744336</v>
+        <v>40.20256848890688</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.24225500323749</v>
+        <v>27.29258617806133</v>
       </c>
       <c r="C5" t="n">
-        <v>35.76016012719008</v>
+        <v>43.71231653158924</v>
       </c>
       <c r="D5" t="n">
-        <v>31.19503330244241</v>
+        <v>29.45243112740432</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.23021198887927</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="C6" t="n">
-        <v>28.2566624236317</v>
+        <v>27.89439752076462</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>18.92416874706152</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.0688619064281</v>
+        <v>7.063398849903775</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15418811106694</v>
+        <v>66.21936421784788</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301646429821075</v>
+        <v>5.297549137427831</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.05403718146258</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C2" t="n">
-        <v>8.442048508818322</v>
+        <v>7.065638227464294</v>
       </c>
       <c r="D2" t="n">
-        <v>34.91880234465055</v>
+        <v>25.33498125579319</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.85232123820225</v>
+        <v>21.50027472300515</v>
       </c>
       <c r="C3" t="n">
-        <v>34.96494448675016</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D3" t="n">
-        <v>74.8877148799467</v>
+        <v>56.94627558483624</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.98864530037232</v>
+        <v>31.97061398879738</v>
       </c>
       <c r="C4" t="n">
-        <v>44.35045253934966</v>
+        <v>51.8804574309227</v>
       </c>
       <c r="D4" t="n">
-        <v>63.36690557061038</v>
+        <v>56.46227396664256</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.94897448157495</v>
+        <v>36.10377182367646</v>
       </c>
       <c r="C5" t="n">
-        <v>54.19247327442395</v>
+        <v>71.93756302868505</v>
       </c>
       <c r="D5" t="n">
-        <v>39.80986940720817</v>
+        <v>38.18998569520093</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.84406634594078</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="C6" t="n">
-        <v>45.12210623488766</v>
+        <v>52.76992085097032</v>
       </c>
       <c r="D6" t="n">
-        <v>33.93214590188251</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>14.01346673041897</v>
       </c>
       <c r="C7" t="n">
-        <v>32.27888276793088</v>
+        <v>30.84160412891355</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.91184799526281</v>
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6227,7 +6227,7 @@
         <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295183926518287</v>
+        <v>7.288883068011984</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51132921925679</v>
+        <v>76.53327221412583</v>
       </c>
       <c r="D21" t="n">
-        <v>6.3832859357035</v>
+        <v>6.377772684510486</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.923063826170254</v>
+        <v>6.136904899246812</v>
       </c>
       <c r="C2" t="n">
-        <v>6.249805885235195</v>
+        <v>4.774239085752239</v>
       </c>
       <c r="D2" t="n">
-        <v>29.04991456866312</v>
+        <v>32.22979538271854</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.98700060013331</v>
+        <v>23.10543221944868</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68376373270807</v>
+        <v>22.64891953697392</v>
       </c>
       <c r="D3" t="n">
-        <v>85.44641143912115</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.49312475163494</v>
+        <v>37.9690924617454</v>
       </c>
       <c r="C4" t="n">
-        <v>70.23324901411257</v>
+        <v>43.12523140444964</v>
       </c>
       <c r="D4" t="n">
-        <v>86.04625928641595</v>
+        <v>71.79030087304801</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>42.80419990516094</v>
       </c>
       <c r="C5" t="n">
-        <v>70.36676670189014</v>
+        <v>85.92746781420209</v>
       </c>
       <c r="D5" t="n">
-        <v>54.33973543006097</v>
+        <v>50.53546307610458</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>68.10580173900973</v>
+        <v>87.18508662334226</v>
       </c>
       <c r="D6" t="n">
-        <v>39.16486116551801</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>24.91282974296706</v>
       </c>
       <c r="C7" t="n">
-        <v>50.36463897556562</v>
+        <v>55.69454726192155</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>34.29735604786232</v>
+        <v>32.46148784092078</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -6510,7 +6510,7 @@
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6538,7 +6538,7 @@
         <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.508775262041696</v>
+        <v>7.50245475707543</v>
       </c>
       <c r="C21" t="n">
-        <v>87.2895124212347</v>
+        <v>86.27822970636744</v>
       </c>
       <c r="D21" t="n">
-        <v>7.508775262041696</v>
+        <v>7.50245475707543</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_92_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633864866</v>
+        <v>10.84497651695956</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907196432722</v>
+        <v>37.78907258564749</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.883033154474388</v>
+        <v>0.4948008429403924</v>
       </c>
       <c r="C2" t="n">
-        <v>4.297109701488289</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="D2" t="n">
-        <v>31.51508305402686</v>
+        <v>16.01230505626548</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.91751749731004</v>
+        <v>5.301437602932776</v>
       </c>
       <c r="C3" t="n">
-        <v>20.2829075697391</v>
+        <v>42.18079011296421</v>
       </c>
       <c r="D3" t="n">
-        <v>74.25939634922874</v>
+        <v>62.44406272861838</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.32568786256524</v>
+        <v>10.73344765053038</v>
       </c>
       <c r="C4" t="n">
-        <v>50.13196476965913</v>
+        <v>131.1241868746125</v>
       </c>
       <c r="D4" t="n">
-        <v>86.86307337634929</v>
+        <v>66.28956848615313</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.53546307610458</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>82.56498192715677</v>
+        <v>121.810346404423</v>
       </c>
       <c r="D5" t="n">
-        <v>63.61725123519332</v>
+        <v>46.4612101034803</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.42903341341842</v>
+        <v>7.3258013690897</v>
       </c>
       <c r="C6" t="n">
-        <v>113.0669013504009</v>
+        <v>67.58253021264619</v>
       </c>
       <c r="D6" t="n">
-        <v>45.36361617013237</v>
+        <v>29.74597369097411</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.00992495469625</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>91.3869667975186</v>
+        <v>39.82459562277186</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>54.07466354991431</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.702243244910774</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.31526015577083</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.665023650524621</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.809222150206629</v>
+        <v>1.293943474197296</v>
       </c>
       <c r="C2" t="n">
-        <v>5.188536616944393</v>
+        <v>6.080945280104743</v>
       </c>
       <c r="D2" t="n">
-        <v>27.10212712343744</v>
+        <v>14.71541633895544</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48202242725196</v>
+        <v>3.387029579651496</v>
       </c>
       <c r="C3" t="n">
-        <v>18.30468594568178</v>
+        <v>24.21971586376881</v>
       </c>
       <c r="D3" t="n">
-        <v>80.5965777801419</v>
+        <v>61.36414025394689</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.64475586644545</v>
+        <v>10.51648140789183</v>
       </c>
       <c r="C4" t="n">
-        <v>49.87671036655495</v>
+        <v>116.651262218606</v>
       </c>
       <c r="D4" t="n">
-        <v>100.7106247447505</v>
+        <v>81.79627347473149</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.76326960121884</v>
+        <v>13.25359400733194</v>
       </c>
       <c r="C5" t="n">
-        <v>87.47372044839082</v>
+        <v>189.2564136861789</v>
       </c>
       <c r="D5" t="n">
-        <v>78.53981633974485</v>
+        <v>59.02758071783948</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.48565598509524</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>121.1172325252248</v>
+        <v>133.4744908785794</v>
       </c>
       <c r="D6" t="n">
-        <v>53.33344403320799</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.02906118716245</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>126.7200666733613</v>
+        <v>69.34869433258619</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.87319998189869</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>86.28580572625216</v>
+        <v>41.22358610132356</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.90009238500763</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.887891927126004</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5145680344196</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.859864908907506</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.659415662084367</v>
+        <v>0.6813329067472864</v>
       </c>
       <c r="C2" t="n">
-        <v>7.204064653763095</v>
+        <v>2.545671797111979</v>
       </c>
       <c r="D2" t="n">
-        <v>27.02064206398496</v>
+        <v>9.947067739428682</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.42235680147115</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="C3" t="n">
-        <v>19.06554041647306</v>
+        <v>25.63343255788422</v>
       </c>
       <c r="D3" t="n">
-        <v>82.33427121665875</v>
+        <v>61.25614800647974</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.4150269036517</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="C4" t="n">
-        <v>47.32416633551325</v>
+        <v>105.4073057618673</v>
       </c>
       <c r="D4" t="n">
-        <v>113.3967685790278</v>
+        <v>92.97641633069418</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.38944471007906</v>
+        <v>13.35176877775663</v>
       </c>
       <c r="C5" t="n">
-        <v>89.36358477906593</v>
+        <v>221.99769962281</v>
       </c>
       <c r="D5" t="n">
-        <v>93.83053683338892</v>
+        <v>66.1943389588412</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.37498053642261</v>
+        <v>9.056622571676828</v>
       </c>
       <c r="C6" t="n">
-        <v>128.2417756149439</v>
+        <v>175.899736169901</v>
       </c>
       <c r="D6" t="n">
-        <v>62.95358978712248</v>
+        <v>37.6755498981756</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.3713723407751</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>149.1775454080071</v>
+        <v>68.15096213340507</v>
       </c>
       <c r="D7" t="n">
-        <v>47.4301950875719</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.88702656521616</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>121.6679929873072</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.30156077611979</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>74.43905617910588</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>45.69544689416779</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>44.860961345558</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.059200660562123</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8288092478697</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08140090827292</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.779769719079225</v>
+        <v>0.3681553890925539</v>
       </c>
       <c r="C2" t="n">
-        <v>4.78307481509046</v>
+        <v>6.66999390265283</v>
       </c>
       <c r="D2" t="n">
-        <v>22.03238197870692</v>
+        <v>10.67650628368406</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.03166227290993</v>
+        <v>3.205406254365836</v>
       </c>
       <c r="C3" t="n">
-        <v>30.36545649235384</v>
+        <v>16.77315952705676</v>
       </c>
       <c r="D3" t="n">
-        <v>89.9379071860503</v>
+        <v>55.77799581678253</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.05245890114836</v>
+        <v>9.776243638889737</v>
       </c>
       <c r="C4" t="n">
-        <v>71.40741926839175</v>
+        <v>83.7489696584784</v>
       </c>
       <c r="D4" t="n">
-        <v>108.3682568378757</v>
+        <v>101.6040151556151</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.38004383919731</v>
+        <v>15.31526418625024</v>
       </c>
       <c r="C5" t="n">
-        <v>76.62540831646356</v>
+        <v>209.8731154753619</v>
       </c>
       <c r="D5" t="n">
-        <v>63.73996969822418</v>
+        <v>82.54043823455059</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.62271544859552</v>
+        <v>13.04153650321463</v>
       </c>
       <c r="C6" t="n">
-        <v>98.25429198872504</v>
+        <v>266.0634453279282</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>48.42274201656544</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.75124228239384</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>85.51807902153115</v>
+        <v>154.8068867441583</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>54.82570054366312</v>
+        <v>63.08710747490004</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.291620125890307</v>
+        <v>0.1688606051304514</v>
       </c>
       <c r="C2" t="n">
-        <v>2.462223242251</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69167446760427</v>
+        <v>8.336019756759667</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.12140222462389</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C3" t="n">
-        <v>24.71549845441345</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>88.38674581334034</v>
+        <v>52.77384784178729</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.63199314629023</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C4" t="n">
-        <v>76.28277836768142</v>
+        <v>65.91944960165209</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4147431373405</v>
+        <v>105.7391364859027</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.30703465618456</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="C5" t="n">
-        <v>104.3352372688298</v>
+        <v>193.4042977366217</v>
       </c>
       <c r="D5" t="n">
-        <v>81.06781667818038</v>
+        <v>94.88591561545424</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.98876847355934</v>
+        <v>15.65789413503238</v>
       </c>
       <c r="C6" t="n">
-        <v>112.9863980386527</v>
+        <v>307.3616442547744</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>58.40515267334701</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>110.251248934621</v>
+        <v>233.8572118901115</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>73.60162538738336</v>
+        <v>98.80308895539899</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>47.92499593051228</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.607742886657781</v>
+        <v>0.2905973204570559</v>
       </c>
       <c r="C2" t="n">
-        <v>6.498188054409638</v>
+        <v>7.897178532961342</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5911352911436</v>
+        <v>13.04840873714436</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.42588288166064</v>
+        <v>1.482439033412684</v>
       </c>
       <c r="C3" t="n">
-        <v>16.46881773874025</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="D3" t="n">
-        <v>81.59305169995241</v>
+        <v>47.71784716491622</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.92325341928206</v>
+        <v>6.611089040398021</v>
       </c>
       <c r="C4" t="n">
-        <v>68.57409539393547</v>
+        <v>60.08688649072178</v>
       </c>
       <c r="D4" t="n">
-        <v>140.4282098677595</v>
+        <v>107.653544509184</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.32086123950202</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C5" t="n">
-        <v>123.8965602759475</v>
+        <v>159.3131087066512</v>
       </c>
       <c r="D5" t="n">
-        <v>105.0470043544087</v>
+        <v>108.6549271675158</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.34853010167018</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C6" t="n">
-        <v>138.6267028304666</v>
+        <v>308.6899488986204</v>
       </c>
       <c r="D6" t="n">
-        <v>52.72966919509619</v>
+        <v>71.60769580005812</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.93196597543326</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>137.3199966361141</v>
+        <v>330.1548807042726</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.44074796594459</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>107.9824299901067</v>
+        <v>188.6771825406732</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>63.89999457401638</v>
+        <v>78.5437433305618</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.28100082759284</v>
+        <v>0.1973312885536089</v>
       </c>
       <c r="C2" t="n">
-        <v>2.946224860444678</v>
+        <v>4.17046424764045</v>
       </c>
       <c r="D2" t="n">
-        <v>10.80413348523615</v>
+        <v>9.498409038587891</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.64186737659494</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C3" t="n">
-        <v>21.55427084673872</v>
+        <v>26.15375884113503</v>
       </c>
       <c r="D3" t="n">
-        <v>79.2270397327176</v>
+        <v>52.48914100755572</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.93900244027901</v>
+        <v>10.40161692649496</v>
       </c>
       <c r="C4" t="n">
-        <v>64.82185566830415</v>
+        <v>87.57778570504097</v>
       </c>
       <c r="D4" t="n">
-        <v>149.7832837415274</v>
+        <v>110.652783745658</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.8979489631499</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C5" t="n">
-        <v>142.279786037969</v>
+        <v>250.2965771977244</v>
       </c>
       <c r="D5" t="n">
-        <v>114.3490638521473</v>
+        <v>101.2672756930585</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.27053006467818</v>
+        <v>7.245298057341462</v>
       </c>
       <c r="C6" t="n">
-        <v>174.4909282143069</v>
+        <v>290.0534322289032</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>61.54478183152831</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.5581157220977</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>145.0453693208322</v>
+        <v>132.6488410593078</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>81.94648087348126</v>
+        <v>57.82984851865836</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.329507375728434</v>
+        <v>0.1079922474671492</v>
       </c>
       <c r="C2" t="n">
-        <v>7.085273181549231</v>
+        <v>2.710605411425443</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7422833798686</v>
+        <v>7.492698478811657</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02979658849267</v>
+        <v>1.428442909679109</v>
       </c>
       <c r="C3" t="n">
-        <v>16.26265072084841</v>
+        <v>20.81796006855362</v>
       </c>
       <c r="D3" t="n">
-        <v>70.90672793922589</v>
+        <v>48.00255399914779</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.91874559138832</v>
+        <v>6.904631603967817</v>
       </c>
       <c r="C4" t="n">
-        <v>59.16797063954677</v>
+        <v>73.71747161648449</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3906257175576</v>
+        <v>107.1302729828204</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.18237805994099</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="C5" t="n">
-        <v>132.3886779176824</v>
+        <v>186.6056948847125</v>
       </c>
       <c r="D5" t="n">
-        <v>137.5428533649782</v>
+        <v>105.660596669563</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>6.84278149860027</v>
       </c>
       <c r="C6" t="n">
-        <v>200.4934979089879</v>
+        <v>282.566624236317</v>
       </c>
       <c r="D6" t="n">
-        <v>71.24543089719104</v>
+        <v>64.24164277509429</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>196.0687610059475</v>
+        <v>183.4925729145458</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>129.4287085893783</v>
+        <v>67.92712365683681</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.34579617607313</v>
+        <v>0.02356194490192345</v>
       </c>
       <c r="C2" t="n">
-        <v>4.567090320156161</v>
+        <v>10.50371868773662</v>
       </c>
       <c r="D2" t="n">
-        <v>8.465610453720245</v>
+        <v>7.923685720976006</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8516993433965</v>
+        <v>0.849211764173491</v>
       </c>
       <c r="C3" t="n">
-        <v>21.90279128174634</v>
+        <v>14.87838645786041</v>
       </c>
       <c r="D3" t="n">
-        <v>65.41384953396498</v>
+        <v>43.31961744989051</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.39248776418302</v>
+        <v>4.722206457427157</v>
       </c>
       <c r="C4" t="n">
-        <v>52.3399153565102</v>
+        <v>61.4524975473291</v>
       </c>
       <c r="D4" t="n">
-        <v>155.1946770873358</v>
+        <v>107.0919848223548</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.95014582239101</v>
+        <v>10.75013736150258</v>
       </c>
       <c r="C5" t="n">
-        <v>127.5535704742669</v>
+        <v>159.0431280879833</v>
       </c>
       <c r="D5" t="n">
-        <v>153.0299233994716</v>
+        <v>118.7669285212579</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.49573550404497</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>214.2998158738108</v>
+        <v>294.1591011280634</v>
       </c>
       <c r="D6" t="n">
-        <v>87.26558993509049</v>
+        <v>82.19388129495147</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>236.4323361183508</v>
+        <v>301.2895347040078</v>
       </c>
       <c r="D7" t="n">
-        <v>44.85507085933252</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>167.3978010511236</v>
+        <v>154.3798264928109</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>57.243745139223</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>22.74218556887735</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.470298208063228</v>
+        <v>0.0755945732270044</v>
       </c>
       <c r="C2" t="n">
-        <v>6.89775937003809</v>
+        <v>13.57658900202914</v>
       </c>
       <c r="D2" t="n">
-        <v>8.706138641260715</v>
+        <v>7.038149291745383</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.11753198706914</v>
+        <v>0.4516039439535328</v>
       </c>
       <c r="C3" t="n">
-        <v>19.72822011683965</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D3" t="n">
-        <v>58.16364273810228</v>
+        <v>39.80496066868693</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.47509344006</v>
+        <v>3.139629158181299</v>
       </c>
       <c r="C4" t="n">
-        <v>53.32264480846126</v>
+        <v>48.21755674637784</v>
       </c>
       <c r="D4" t="n">
-        <v>152.7569975376909</v>
+        <v>104.7819324742621</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.14020396638739</v>
+        <v>9.203884727313849</v>
       </c>
       <c r="C5" t="n">
-        <v>113.2691413774758</v>
+        <v>135.7266201121216</v>
       </c>
       <c r="D5" t="n">
-        <v>169.3023915973625</v>
+        <v>129.3698037271235</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79.98004022187492</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>212.3274847359789</v>
+        <v>275.4420811465979</v>
       </c>
       <c r="D6" t="n">
-        <v>108.1159476778843</v>
+        <v>97.57001383886501</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.13643153982385</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>268.5914456663636</v>
+        <v>363.9309287211799</v>
       </c>
       <c r="D7" t="n">
-        <v>55.21545438224911</v>
+        <v>55.81432048183967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>229.31662875797</v>
+        <v>271.3747004079033</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>124.1390519588964</v>
+        <v>119.479677354541</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>24.62812290873548</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.097455064627692</v>
+        <v>1.701368771459722</v>
       </c>
       <c r="C2" t="n">
-        <v>3.887720908817369</v>
+        <v>8.161268665403735</v>
       </c>
       <c r="D2" t="n">
-        <v>6.026949156371169</v>
+        <v>14.02622945057418</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.829797794266807</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C2" t="n">
-        <v>3.808199344773377</v>
+        <v>20.88962765096363</v>
       </c>
       <c r="D2" t="n">
-        <v>6.406885517914684</v>
+        <v>11.28028112179585</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.39933463591697</v>
+        <v>0.3485204350076177</v>
       </c>
       <c r="C3" t="n">
-        <v>25.02965771977243</v>
+        <v>40.34001316750144</v>
       </c>
       <c r="D3" t="n">
-        <v>62.00718500022854</v>
+        <v>36.59955441432109</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.23705283174254</v>
+        <v>2.042035224833366</v>
       </c>
       <c r="C4" t="n">
-        <v>74.54704842657306</v>
+        <v>59.15520791939156</v>
       </c>
       <c r="D4" t="n">
-        <v>158.1301027230338</v>
+        <v>100.3915567408703</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.42470551197393</v>
+        <v>7.387651474457249</v>
       </c>
       <c r="C5" t="n">
-        <v>175.0701593598125</v>
+        <v>113.9072773852362</v>
       </c>
       <c r="D5" t="n">
-        <v>155.1652246562084</v>
+        <v>136.512018275519</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.37112599440108</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>222.6721602956276</v>
+        <v>247.8696968728262</v>
       </c>
       <c r="D6" t="n">
-        <v>85.29325879725866</v>
+        <v>112.744888103408</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.503898614185871</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>161.2746406197363</v>
+        <v>383.0946439080776</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>66.95322993422397</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>91.45961612763286</v>
+        <v>365.9219130653924</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>210.4484196300505</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>85.5544036865883</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.483862749473436</v>
+        <v>2.970768553050848</v>
       </c>
       <c r="C2" t="n">
-        <v>4.636794407157685</v>
+        <v>7.114725612676635</v>
       </c>
       <c r="D2" t="n">
-        <v>17.18353006743192</v>
+        <v>15.18174649847268</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19040230136165</v>
+        <v>2.827433388230814</v>
       </c>
       <c r="C3" t="n">
-        <v>9.950012982541423</v>
+        <v>16.11047982669016</v>
       </c>
       <c r="D3" t="n">
-        <v>8.197593330460867</v>
+        <v>12.57127935288041</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39891066391973</v>
+        <v>11.67798772241532</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14723818169743</v>
+        <v>59.94700364173196</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57634243104938</v>
+        <v>0.7785325148276877</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.557673753741193</v>
+        <v>1.965458903902114</v>
       </c>
       <c r="C2" t="n">
-        <v>6.290057541109315</v>
+        <v>5.071708640139023</v>
       </c>
       <c r="D2" t="n">
-        <v>13.90841972606456</v>
+        <v>14.34726094986289</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.44275251908209</v>
+        <v>7.520187414530567</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0354660905399</v>
+        <v>23.91046533693107</v>
       </c>
       <c r="D3" t="n">
-        <v>20.65106295883166</v>
+        <v>22.77163800000477</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.84602984134927</v>
+        <v>3.75223972563131</v>
       </c>
       <c r="C4" t="n">
-        <v>15.6981457909065</v>
+        <v>26.73789872516188</v>
       </c>
       <c r="D4" t="n">
-        <v>19.36104647545135</v>
+        <v>20.89257289407637</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44294571924592</v>
+        <v>13.6304131091135</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15538138105622</v>
+        <v>73.76458859049661</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251146467209669</v>
+        <v>1.603578012836883</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.764822519337271</v>
+        <v>1.493238258159398</v>
       </c>
       <c r="C2" t="n">
-        <v>8.751299035656068</v>
+        <v>10.2033038902371</v>
       </c>
       <c r="D2" t="n">
-        <v>29.51428123277186</v>
+        <v>16.89489624238336</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.64124548178919</v>
+        <v>7.161849502480482</v>
       </c>
       <c r="C3" t="n">
-        <v>20.75905520629881</v>
+        <v>21.26956401250715</v>
       </c>
       <c r="D3" t="n">
-        <v>26.98333565122358</v>
+        <v>29.31989518733099</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.14478424307656</v>
+        <v>10.22293884432204</v>
       </c>
       <c r="C4" t="n">
-        <v>28.61401858797754</v>
+        <v>47.60494617892783</v>
       </c>
       <c r="D4" t="n">
-        <v>25.35952494839936</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.13149743910684</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="C5" t="n">
-        <v>18.77592484372025</v>
+        <v>32.07860623626453</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>27.66074156715389</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73980098587779</v>
+        <v>14.84484719421991</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1127860138545</v>
+        <v>87.41965569929501</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021940295763338</v>
+        <v>2.474141199036651</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.578290455530377</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C2" t="n">
-        <v>4.82921695719006</v>
+        <v>8.397869862127216</v>
       </c>
       <c r="D2" t="n">
-        <v>21.74571164906685</v>
+        <v>18.25363506506094</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.15528036818702</v>
+        <v>6.03283964259665</v>
       </c>
       <c r="C3" t="n">
-        <v>28.36759991421159</v>
+        <v>32.65292864324891</v>
       </c>
       <c r="D3" t="n">
-        <v>43.41288348179395</v>
+        <v>36.03014074585794</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.01188845010475</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C4" t="n">
-        <v>41.37673874318607</v>
+        <v>51.03811790067893</v>
       </c>
       <c r="D4" t="n">
-        <v>32.7491399182651</v>
+        <v>35.95258267722244</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.28124717396688</v>
+        <v>10.11200135374215</v>
       </c>
       <c r="C5" t="n">
-        <v>37.50276230222816</v>
+        <v>64.50082416901546</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56318869153496</v>
+        <v>31.75953823238432</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.57109942643116</v>
+        <v>5.27296691950962</v>
       </c>
       <c r="C6" t="n">
-        <v>21.49438423677967</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06815078394659</v>
+        <v>16.09377525367171</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8731741619373</v>
+        <v>101.6448963389792</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883105060551082</v>
+        <v>3.388163211299308</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.813329067472864</v>
+        <v>1.374446785945534</v>
       </c>
       <c r="C2" t="n">
-        <v>2.895173979823844</v>
+        <v>12.6341112059522</v>
       </c>
       <c r="D2" t="n">
-        <v>24.46024405130928</v>
+        <v>21.88217457995716</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.62728002975148</v>
+        <v>5.011822030179967</v>
       </c>
       <c r="C3" t="n">
-        <v>21.47082229187775</v>
+        <v>32.62347621212151</v>
       </c>
       <c r="D3" t="n">
-        <v>47.30551312913256</v>
+        <v>41.88626580169017</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.58023825540564</v>
+        <v>12.13734686760332</v>
       </c>
       <c r="C4" t="n">
-        <v>48.20479402622264</v>
+        <v>68.49751907300421</v>
       </c>
       <c r="D4" t="n">
-        <v>40.20256848890688</v>
+        <v>45.03963942773092</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.29258617806133</v>
+        <v>14.60349710067131</v>
       </c>
       <c r="C5" t="n">
-        <v>43.71231653158924</v>
+        <v>80.28241851478293</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45243112740432</v>
+        <v>37.60093707265284</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.50317890838889</v>
+        <v>9.499390786292139</v>
       </c>
       <c r="C6" t="n">
-        <v>27.89439752076462</v>
+        <v>70.3196428120863</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.467753875577986</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>16.94791061841269</v>
+        <v>33.53650157707104</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063398849903775</v>
+        <v>17.37098392632179</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21936421784788</v>
+        <v>115.5170431100399</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297549137427831</v>
+        <v>4.342745981580447</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.975317438673588</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C2" t="n">
-        <v>7.065638227464294</v>
+        <v>11.22824849347077</v>
       </c>
       <c r="D2" t="n">
-        <v>25.33498125579319</v>
+        <v>30.86222083070273</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.50027472300515</v>
+        <v>4.82038122785184</v>
       </c>
       <c r="C3" t="n">
-        <v>14.82929907264807</v>
+        <v>41.69482499936204</v>
       </c>
       <c r="D3" t="n">
-        <v>56.94627558483624</v>
+        <v>48.7241385617692</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.97061398879738</v>
+        <v>10.88660029239288</v>
       </c>
       <c r="C4" t="n">
-        <v>51.8804574309227</v>
+        <v>75.52977787852411</v>
       </c>
       <c r="D4" t="n">
-        <v>56.46227396664256</v>
+        <v>54.2670860999467</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.10377182367646</v>
+        <v>16.37064296831556</v>
       </c>
       <c r="C5" t="n">
-        <v>71.93756302868505</v>
+        <v>104.2861498836175</v>
       </c>
       <c r="D5" t="n">
-        <v>38.18998569520093</v>
+        <v>44.91495746929158</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.57867567062465</v>
+        <v>14.53084777055704</v>
       </c>
       <c r="C6" t="n">
-        <v>52.76992085097032</v>
+        <v>98.33479530047329</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.01346673041897</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>30.84160412891355</v>
+        <v>67.61198264377359</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>21.19593293468863</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288883068011984</v>
+        <v>18.66842095782871</v>
       </c>
       <c r="C21" t="n">
-        <v>76.53327221412583</v>
+        <v>128.9010018516744</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377772684510486</v>
+        <v>5.333834559379631</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.136904899246812</v>
+        <v>0.9444412914854315</v>
       </c>
       <c r="C2" t="n">
-        <v>4.774239085752239</v>
+        <v>6.826091787628073</v>
       </c>
       <c r="D2" t="n">
-        <v>32.22979538271854</v>
+        <v>24.13528556120359</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.10543221944868</v>
+        <v>6.931138791982481</v>
       </c>
       <c r="C3" t="n">
-        <v>22.64891953697392</v>
+        <v>60.28421777927539</v>
       </c>
       <c r="D3" t="n">
-        <v>64.00013283984957</v>
+        <v>55.35093556543517</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.9690924617454</v>
+        <v>7.861835615608458</v>
       </c>
       <c r="C4" t="n">
-        <v>43.12523140444964</v>
+        <v>99.90657337497241</v>
       </c>
       <c r="D4" t="n">
-        <v>71.79030087304801</v>
+        <v>52.45477983790708</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.80419990516094</v>
+        <v>8.173049637854698</v>
       </c>
       <c r="C5" t="n">
-        <v>85.92746781420209</v>
+        <v>58.75760009917161</v>
       </c>
       <c r="D5" t="n">
-        <v>50.53546307610458</v>
+        <v>37.40458753180348</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>87.18508662334226</v>
+        <v>44.51833139677587</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>25.55980148006571</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.91282974296706</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>55.69454726192155</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>32.46148784092078</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.50245475707543</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.27822970636744</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.50245475707543</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
